--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
   <si>
     <t>ID</t>
   </si>
@@ -231,6 +231,30 @@
   </si>
   <si>
     <t>0,0;0,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -974,14 +998,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:H23" totalsRowShown="0">
-  <autoFilter ref="A1:H23"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:I23" totalsRowShown="0">
+  <autoFilter ref="A1:I23"/>
+  <tableColumns count="9">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="8" name="Name"/>
     <tableColumn id="6" name="EngineId"/>
     <tableColumn id="5" name="DisplayName"/>
     <tableColumn id="2" name="Type"/>
+    <tableColumn id="9" name="Icon"/>
     <tableColumn id="3" name="Level"/>
     <tableColumn id="4" name="Coordinates"/>
     <tableColumn id="7" name="Desc"/>
@@ -1253,17 +1278,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.75" customWidth="1"/>
     <col min="3" max="3" width="18.375" customWidth="1"/>
     <col min="4" max="4" width="13.375" customWidth="1"/>
-    <col min="7" max="7" width="35.875" customWidth="1"/>
+    <col min="6" max="6" width="18.375" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="34.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1280,16 +1306,19 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>201001</v>
       </c>
@@ -1305,17 +1334,20 @@
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>55</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>201002</v>
       </c>
@@ -1331,17 +1363,20 @@
       <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>56</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>201003</v>
       </c>
@@ -1357,17 +1392,20 @@
       <c r="E4" t="s">
         <v>4</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>58</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>201004</v>
       </c>
@@ -1383,17 +1421,20 @@
       <c r="E5" t="s">
         <v>4</v>
       </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
         <v>60</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>202001</v>
       </c>
@@ -1409,17 +1450,20 @@
       <c r="E6" t="s">
         <v>4</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>55</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>202002</v>
       </c>
@@ -1435,17 +1479,20 @@
       <c r="E7" t="s">
         <v>4</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7">
         <v>2</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>61</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>202003</v>
       </c>
@@ -1461,17 +1508,20 @@
       <c r="E8" t="s">
         <v>4</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8">
         <v>3</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>57</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>202004</v>
       </c>
@@ -1487,17 +1537,20 @@
       <c r="E9" t="s">
         <v>4</v>
       </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="F9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="H9" t="s">
         <v>59</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>203001</v>
       </c>
@@ -1513,17 +1566,20 @@
       <c r="E10" t="s">
         <v>4</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>55</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>203002</v>
       </c>
@@ -1539,17 +1595,20 @@
       <c r="E11" t="s">
         <v>4</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11">
         <v>2</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>56</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>203003</v>
       </c>
@@ -1565,17 +1624,20 @@
       <c r="E12" t="s">
         <v>4</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12">
         <v>3</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>58</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>203004</v>
       </c>
@@ -1591,17 +1653,20 @@
       <c r="E13" t="s">
         <v>4</v>
       </c>
-      <c r="F13">
-        <v>4</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="F13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13" t="s">
         <v>60</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>204001</v>
       </c>
@@ -1617,17 +1682,20 @@
       <c r="E14" t="s">
         <v>4</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>55</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>204002</v>
       </c>
@@ -1643,17 +1711,20 @@
       <c r="E15" t="s">
         <v>4</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15">
         <v>2</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>56</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>204003</v>
       </c>
@@ -1669,17 +1740,20 @@
       <c r="E16" t="s">
         <v>4</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16">
         <v>3</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>58</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>204004</v>
       </c>
@@ -1695,17 +1769,20 @@
       <c r="E17" t="s">
         <v>4</v>
       </c>
-      <c r="F17">
-        <v>4</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="F17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17">
+        <v>4</v>
+      </c>
+      <c r="H17" t="s">
         <v>60</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>205001</v>
       </c>
@@ -1721,17 +1798,20 @@
       <c r="E18" t="s">
         <v>4</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>55</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>205002</v>
       </c>
@@ -1747,17 +1827,20 @@
       <c r="E19" t="s">
         <v>4</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19">
         <v>2</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>56</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>205003</v>
       </c>
@@ -1773,17 +1856,20 @@
       <c r="E20" t="s">
         <v>4</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20">
         <v>3</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>58</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>205004</v>
       </c>
@@ -1799,17 +1885,20 @@
       <c r="E21" t="s">
         <v>4</v>
       </c>
-      <c r="F21">
-        <v>4</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="F21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21" t="s">
         <v>60</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>211001</v>
       </c>
@@ -1821,15 +1910,18 @@
       <c r="E22" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="2">
         <v>1</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>211002</v>
       </c>
@@ -1841,13 +1933,16 @@
       <c r="E23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="6">
         <v>2</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
-  <si>
-    <t>ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="67">
   <si>
     <t>Type</t>
   </si>
@@ -37,176 +34,180 @@
     <t>normal</t>
   </si>
   <si>
-    <t>special</t>
+    <t>DisplayName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EngineId</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.2</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.3</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.4</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.2</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.3</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.4</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.2</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.3</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.4</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.2</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.3</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.4</t>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">엔진 위치의 상부 시설을 작동시킵니다. </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreenEngine_1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreenEngine_2</t>
+  </si>
+  <si>
+    <t>GreenEngine_3</t>
+  </si>
+  <si>
+    <t>GreenEngine_4</t>
+  </si>
+  <si>
+    <t>RedEngine_1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RedEngine_2</t>
+  </si>
+  <si>
+    <t>RedEngine_3</t>
+  </si>
+  <si>
+    <t>RedEngine_4</t>
+  </si>
+  <si>
+    <t>BlueEngine_1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BlueEngine_2</t>
+  </si>
+  <si>
+    <t>BlueEngine_3</t>
+  </si>
+  <si>
+    <t>BlueEngine_4</t>
+  </si>
+  <si>
+    <t>PurpleEngine_1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PurpleEngine_2</t>
+  </si>
+  <si>
+    <t>PurpleEngine_3</t>
+  </si>
+  <si>
+    <t>PurpleEngine_4</t>
+  </si>
+  <si>
+    <t>YellowEngine_1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>YellowEngine_2</t>
+  </si>
+  <si>
+    <t>YellowEngine_3</t>
+  </si>
+  <si>
+    <t>YellowEngine_4</t>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>0,0;0,1</t>
-  </si>
-  <si>
-    <t>1,0;1,1</t>
-  </si>
-  <si>
-    <t>DisplayName</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>초록 엔진 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>초록 엔진 Lv.2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>초록 엔진 Lv.3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>초록 엔진 Lv.4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EngineId</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>빨강 엔진 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>빨강 엔진 Lv.2</t>
-  </si>
-  <si>
-    <t>빨강 엔진 Lv.3</t>
-  </si>
-  <si>
-    <t>빨강 엔진 Lv.4</t>
-  </si>
-  <si>
-    <t>파랑 엔진 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>파랑 엔진 Lv.2</t>
-  </si>
-  <si>
-    <t>파랑 엔진 Lv.3</t>
-  </si>
-  <si>
-    <t>파랑 엔진 Lv.4</t>
-  </si>
-  <si>
-    <t>보라 엔진 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>보라 엔진 Lv.2</t>
-  </si>
-  <si>
-    <t>보라 엔진 Lv.3</t>
-  </si>
-  <si>
-    <t>보라 엔진 Lv.4</t>
-  </si>
-  <si>
-    <t>노랑 엔진 Lv.1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>노랑 엔진 Lv.2</t>
-  </si>
-  <si>
-    <t>노랑 엔진 Lv.3</t>
-  </si>
-  <si>
-    <t>노랑 엔진 Lv.4</t>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">엔진 위치의 상부 시설을 작동시킵니다. </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>GreenEngine_1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>GreenEngine_2</t>
-  </si>
-  <si>
-    <t>GreenEngine_3</t>
-  </si>
-  <si>
-    <t>GreenEngine_4</t>
-  </si>
-  <si>
-    <t>RedEngine_1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RedEngine_2</t>
-  </si>
-  <si>
-    <t>RedEngine_3</t>
-  </si>
-  <si>
-    <t>RedEngine_4</t>
-  </si>
-  <si>
-    <t>BlueEngine_1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>BlueEngine_2</t>
-  </si>
-  <si>
-    <t>BlueEngine_3</t>
-  </si>
-  <si>
-    <t>BlueEngine_4</t>
-  </si>
-  <si>
-    <t>PurpleEngine_1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PurpleEngine_2</t>
-  </si>
-  <si>
-    <t>PurpleEngine_3</t>
-  </si>
-  <si>
-    <t>PurpleEngine_4</t>
-  </si>
-  <si>
-    <t>YellowEngine_1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>YellowEngine_2</t>
-  </si>
-  <si>
-    <t>YellowEngine_3</t>
-  </si>
-  <si>
-    <t>YellowEngine_4</t>
-  </si>
-  <si>
-    <t>SpecialEngine_1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>SpecialEngine_2</t>
-  </si>
-  <si>
-    <t>0,0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2;1,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2;1,2</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -214,26 +215,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>0,0;0,1;0,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;0,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;0,2;1,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;0,2;1,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -255,6 +236,26 @@
   </si>
   <si>
     <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Core</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>core</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>코어</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>코어.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -610,7 +611,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -762,26 +763,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -911,7 +892,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -927,16 +908,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -998,10 +970,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:I23" totalsRowShown="0">
-  <autoFilter ref="A1:I23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:I22" totalsRowShown="0">
+  <autoFilter ref="A1:I22"/>
   <tableColumns count="9">
-    <tableColumn id="1" name="ID"/>
+    <tableColumn id="1" name="Id"/>
     <tableColumn id="8" name="Name"/>
     <tableColumn id="6" name="EngineId"/>
     <tableColumn id="5" name="DisplayName"/>
@@ -1278,7 +1250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.75" customWidth="1"/>
@@ -1291,31 +1263,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
       <c r="I1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -1323,28 +1295,28 @@
         <v>201001</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>201</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -1352,28 +1324,28 @@
         <v>201002</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>201</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -1381,28 +1353,28 @@
         <v>201003</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -1410,28 +1382,28 @@
         <v>201004</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>201</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -1439,28 +1411,28 @@
         <v>202001</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>202</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1468,28 +1440,28 @@
         <v>202002</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>202</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1497,28 +1469,28 @@
         <v>202003</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>202</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -1526,28 +1498,28 @@
         <v>202004</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>202</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -1555,28 +1527,28 @@
         <v>203001</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>203</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -1584,28 +1556,28 @@
         <v>203002</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>203</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1613,28 +1585,28 @@
         <v>203003</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>203</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I12" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1642,28 +1614,28 @@
         <v>203004</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C13">
         <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1671,28 +1643,28 @@
         <v>204001</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1700,28 +1672,28 @@
         <v>204002</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C15">
         <v>204</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1729,28 +1701,28 @@
         <v>204003</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>204</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G16">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1758,28 +1730,28 @@
         <v>204004</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G17">
         <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1787,28 +1759,28 @@
         <v>205001</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>205</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1816,28 +1788,28 @@
         <v>205002</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>205</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1845,28 +1817,28 @@
         <v>205003</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>205</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G20">
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I20" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1874,75 +1846,58 @@
         <v>205004</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>205</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G21">
         <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I21" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>211001</v>
+        <v>202001</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2001</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E22" s="2" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
-        <v>211002</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="6">
-        <v>2</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" s="8"/>
+      <c r="H22" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>

--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -1872,7 +1872,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <v>202001</v>
+        <v>210001</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>62</v>

--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6F76A6-003A-496A-A412-B9FFF1F4D0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16170" windowHeight="9585"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Engine_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="79">
   <si>
     <t>Type</t>
   </si>
@@ -31,9 +32,6 @@
     <t>Coordinates</t>
   </si>
   <si>
-    <t>normal</t>
-  </si>
-  <si>
     <t>DisplayName</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -256,13 +254,65 @@
   </si>
   <si>
     <t>Id</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Length</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainCoordinate</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Green</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Red</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blue</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Purple</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yellow</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -896,19 +946,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -970,18 +1020,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:I22" totalsRowShown="0">
-  <autoFilter ref="A1:I22"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="8" name="Name"/>
-    <tableColumn id="6" name="EngineId"/>
-    <tableColumn id="5" name="DisplayName"/>
-    <tableColumn id="2" name="Type"/>
-    <tableColumn id="9" name="Icon"/>
-    <tableColumn id="3" name="Level"/>
-    <tableColumn id="4" name="Coordinates"/>
-    <tableColumn id="7" name="Desc"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:K22" totalsRowShown="0">
+  <autoFilter ref="A1:K22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Name"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EngineId"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DisplayName"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Icon"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Desc"/>
+    <tableColumn id="10" xr3:uid="{26779C70-3AA8-4F94-983F-B5C4082C3A51}" name="Length"/>
+    <tableColumn id="11" xr3:uid="{0CBADE81-D0CF-4FA8-B9B2-7600A090BEE8}" name="MainCoordinate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1249,8 +1301,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.75" customWidth="1"/>
@@ -1259,26 +1311,28 @@
     <col min="6" max="6" width="18.375" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="34.625" customWidth="1"/>
+    <col min="9" max="9" width="37.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G1" t="s">
         <v>1</v>
@@ -1287,616 +1341,748 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>201001</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>201</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>201002</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>201</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>201003</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>201004</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>201</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J5" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>202001</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>202</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>202002</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>202</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>202003</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>202</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>202004</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>202</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>203001</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>203</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>203002</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>203</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>2</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>203003</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>203</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>3</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>203004</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J13" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>204001</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14">
         <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>204002</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>204</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J15" t="s">
+        <v>68</v>
+      </c>
+      <c r="K15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>204003</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>204</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G16">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J16" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>204004</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G17">
         <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J17" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>205001</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>205</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J18" t="s">
+        <v>67</v>
+      </c>
+      <c r="K18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>205002</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>205</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G19">
         <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J19" t="s">
+        <v>68</v>
+      </c>
+      <c r="K19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>205003</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20">
         <v>205</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20">
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>205004</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>205</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G21">
         <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="J21" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>210001</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2">
         <v>2001</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
+      </c>
+      <c r="J22" t="s">
+        <v>67</v>
+      </c>
+      <c r="K22" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD6F76A6-003A-496A-A412-B9FFF1F4D0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Engine_Data" sheetId="1" r:id="rId1"/>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="81">
   <si>
     <t>Type</t>
   </si>
@@ -306,13 +305,21 @@
   </si>
   <si>
     <t>Yellow</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceItemId</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceItemCount</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1020,20 +1027,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:K22" totalsRowShown="0">
-  <autoFilter ref="A1:K22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Name"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EngineId"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DisplayName"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Icon"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Desc"/>
-    <tableColumn id="10" xr3:uid="{26779C70-3AA8-4F94-983F-B5C4082C3A51}" name="Length"/>
-    <tableColumn id="11" xr3:uid="{0CBADE81-D0CF-4FA8-B9B2-7600A090BEE8}" name="MainCoordinate"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:M22" totalsRowShown="0">
+  <autoFilter ref="A1:M22"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="8" name="Name"/>
+    <tableColumn id="6" name="EngineId"/>
+    <tableColumn id="5" name="DisplayName"/>
+    <tableColumn id="2" name="Type"/>
+    <tableColumn id="9" name="Icon"/>
+    <tableColumn id="3" name="Level"/>
+    <tableColumn id="4" name="Coordinates"/>
+    <tableColumn id="7" name="Desc"/>
+    <tableColumn id="12" name="ResourceItemId"/>
+    <tableColumn id="13" name="ResourceItemCount"/>
+    <tableColumn id="10" name="Length"/>
+    <tableColumn id="11" name="MainCoordinate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1301,8 +1310,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.75" customWidth="1"/>
@@ -1312,10 +1321,11 @@
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="34.625" customWidth="1"/>
     <col min="9" max="9" width="37.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.625" customWidth="1"/>
+    <col min="10" max="10" width="22.125" customWidth="1"/>
+    <col min="11" max="11" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>65</v>
       </c>
@@ -1344,13 +1354,19 @@
         <v>25</v>
       </c>
       <c r="J1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1" t="s">
         <v>66</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>201001</v>
       </c>
@@ -1378,14 +1394,20 @@
       <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2">
+        <v>1002</v>
+      </c>
+      <c r="K2">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="s">
         <v>67</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>201002</v>
       </c>
@@ -1413,14 +1435,20 @@
       <c r="I3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3">
+        <v>1004</v>
+      </c>
+      <c r="K3">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="s">
         <v>68</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>201003</v>
       </c>
@@ -1448,14 +1476,20 @@
       <c r="I4" t="s">
         <v>26</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4">
+        <v>1006</v>
+      </c>
+      <c r="K4">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="s">
         <v>69</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>201004</v>
       </c>
@@ -1483,14 +1517,20 @@
       <c r="I5" t="s">
         <v>26</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5">
+        <v>1008</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+      <c r="L5" t="s">
         <v>70</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>202001</v>
       </c>
@@ -1518,14 +1558,20 @@
       <c r="I6" t="s">
         <v>26</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6">
+        <v>1002</v>
+      </c>
+      <c r="K6">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="s">
         <v>67</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>202002</v>
       </c>
@@ -1553,14 +1599,20 @@
       <c r="I7" t="s">
         <v>26</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7">
+        <v>1004</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="s">
         <v>68</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>202003</v>
       </c>
@@ -1588,14 +1640,20 @@
       <c r="I8" t="s">
         <v>26</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8">
+        <v>1006</v>
+      </c>
+      <c r="K8">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="s">
         <v>69</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>202004</v>
       </c>
@@ -1623,14 +1681,20 @@
       <c r="I9" t="s">
         <v>26</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9">
+        <v>1008</v>
+      </c>
+      <c r="K9">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="s">
         <v>70</v>
       </c>
-      <c r="K9" t="s">
+      <c r="M9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>203001</v>
       </c>
@@ -1658,14 +1722,20 @@
       <c r="I10" t="s">
         <v>26</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10">
+        <v>1002</v>
+      </c>
+      <c r="K10">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="s">
         <v>67</v>
       </c>
-      <c r="K10" t="s">
+      <c r="M10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>203002</v>
       </c>
@@ -1693,14 +1763,20 @@
       <c r="I11" t="s">
         <v>26</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11">
+        <v>1004</v>
+      </c>
+      <c r="K11">
+        <v>1000</v>
+      </c>
+      <c r="L11" t="s">
         <v>68</v>
       </c>
-      <c r="K11" t="s">
+      <c r="M11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>203003</v>
       </c>
@@ -1728,14 +1804,20 @@
       <c r="I12" t="s">
         <v>26</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12">
+        <v>1006</v>
+      </c>
+      <c r="K12">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="s">
         <v>69</v>
       </c>
-      <c r="K12" t="s">
+      <c r="M12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>203004</v>
       </c>
@@ -1763,14 +1845,20 @@
       <c r="I13" t="s">
         <v>26</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13">
+        <v>1008</v>
+      </c>
+      <c r="K13">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="s">
         <v>70</v>
       </c>
-      <c r="K13" t="s">
+      <c r="M13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>204001</v>
       </c>
@@ -1798,14 +1886,20 @@
       <c r="I14" t="s">
         <v>26</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14">
+        <v>1002</v>
+      </c>
+      <c r="K14">
+        <v>1000</v>
+      </c>
+      <c r="L14" t="s">
         <v>67</v>
       </c>
-      <c r="K14" t="s">
+      <c r="M14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>204002</v>
       </c>
@@ -1833,14 +1927,20 @@
       <c r="I15" t="s">
         <v>26</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15">
+        <v>1004</v>
+      </c>
+      <c r="K15">
+        <v>1000</v>
+      </c>
+      <c r="L15" t="s">
         <v>68</v>
       </c>
-      <c r="K15" t="s">
+      <c r="M15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>204003</v>
       </c>
@@ -1868,14 +1968,20 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16">
+        <v>1006</v>
+      </c>
+      <c r="K16">
+        <v>1000</v>
+      </c>
+      <c r="L16" t="s">
         <v>69</v>
       </c>
-      <c r="K16" t="s">
+      <c r="M16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>204004</v>
       </c>
@@ -1903,14 +2009,20 @@
       <c r="I17" t="s">
         <v>26</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17">
+        <v>1008</v>
+      </c>
+      <c r="K17">
+        <v>1000</v>
+      </c>
+      <c r="L17" t="s">
         <v>70</v>
       </c>
-      <c r="K17" t="s">
+      <c r="M17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>205001</v>
       </c>
@@ -1938,14 +2050,20 @@
       <c r="I18" t="s">
         <v>26</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18">
+        <v>1002</v>
+      </c>
+      <c r="K18">
+        <v>1000</v>
+      </c>
+      <c r="L18" t="s">
         <v>67</v>
       </c>
-      <c r="K18" t="s">
+      <c r="M18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>205002</v>
       </c>
@@ -1973,14 +2091,20 @@
       <c r="I19" t="s">
         <v>26</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19">
+        <v>1004</v>
+      </c>
+      <c r="K19">
+        <v>1000</v>
+      </c>
+      <c r="L19" t="s">
         <v>68</v>
       </c>
-      <c r="K19" t="s">
+      <c r="M19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>205003</v>
       </c>
@@ -2008,14 +2132,20 @@
       <c r="I20" t="s">
         <v>26</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20">
+        <v>1006</v>
+      </c>
+      <c r="K20">
+        <v>1000</v>
+      </c>
+      <c r="L20" t="s">
         <v>69</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>205004</v>
       </c>
@@ -2043,14 +2173,20 @@
       <c r="I21" t="s">
         <v>26</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21">
+        <v>1008</v>
+      </c>
+      <c r="K21">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="s">
         <v>70</v>
       </c>
-      <c r="K21" t="s">
+      <c r="M21" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>210001</v>
       </c>
@@ -2078,10 +2214,12 @@
       <c r="I22" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" t="s">
         <v>67</v>
       </c>
-      <c r="K22" t="s">
+      <c r="M22" t="s">
         <v>48</v>
       </c>
     </row>

--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0951BAD-7CB4-49C9-A441-FEE2D9816647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Engine_Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="105">
   <si>
     <t>Type</t>
   </si>
@@ -314,12 +315,84 @@
   <si>
     <t>ResourceItemCount</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreenEngine_5</t>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>GreenEngine_6</t>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>GreenEngine_7</t>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>RedEngine_5</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>RedEngine_6</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>RedEngine_7</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>BlueEngine_5</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>BlueEngine_6</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>BlueEngine_7</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>PurpleEngine_5</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>PurpleEngine_6</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>PurpleEngine_7</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1027,22 +1100,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:M22" totalsRowShown="0">
-  <autoFilter ref="A1:M22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:M34" totalsRowShown="0">
+  <autoFilter ref="A1:M34" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" name="Id"/>
-    <tableColumn id="8" name="Name"/>
-    <tableColumn id="6" name="EngineId"/>
-    <tableColumn id="5" name="DisplayName"/>
-    <tableColumn id="2" name="Type"/>
-    <tableColumn id="9" name="Icon"/>
-    <tableColumn id="3" name="Level"/>
-    <tableColumn id="4" name="Coordinates"/>
-    <tableColumn id="7" name="Desc"/>
-    <tableColumn id="12" name="ResourceItemId"/>
-    <tableColumn id="13" name="ResourceItemCount"/>
-    <tableColumn id="10" name="Length"/>
-    <tableColumn id="11" name="MainCoordinate"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Name"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EngineId"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DisplayName"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Icon"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Desc"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="ResourceItemId"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="ResourceItemCount"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Length"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="MainCoordinate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1310,8 +1383,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.75" customWidth="1"/>
@@ -1532,204 +1605,159 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>202001</v>
+        <v>201005</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="C6">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
-      </c>
-      <c r="J6">
-        <v>1002</v>
-      </c>
-      <c r="K6">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M6" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>202002</v>
+        <v>201006</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="C7">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
-      </c>
-      <c r="J7">
-        <v>1004</v>
-      </c>
-      <c r="K7">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="s">
-        <v>68</v>
-      </c>
-      <c r="M7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>202003</v>
+        <v>201007</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C8">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
-      </c>
-      <c r="J8">
-        <v>1006</v>
-      </c>
-      <c r="K8">
-        <v>1000</v>
-      </c>
-      <c r="L8" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>202004</v>
+        <v>202001</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>202</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
       </c>
       <c r="J9">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="K9">
         <v>1000</v>
       </c>
       <c r="L9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="M9" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>203001</v>
+        <v>202002</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C10">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
       </c>
       <c r="J10">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="K10">
         <v>1000</v>
       </c>
       <c r="L10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M10" t="s">
         <v>48</v>
@@ -1737,489 +1765,846 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>203002</v>
+        <v>202003</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C11">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
       </c>
       <c r="J11">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="K11">
         <v>1000</v>
       </c>
       <c r="L11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M11" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>203003</v>
+        <v>202004</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>57</v>
+        <v>75</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
       </c>
       <c r="J12">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="K12">
         <v>1000</v>
       </c>
       <c r="L12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>203004</v>
+        <v>202005</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="C13">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>60</v>
+        <v>75</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="G13">
-        <v>4</v>
-      </c>
-      <c r="H13" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
-      </c>
-      <c r="J13">
-        <v>1008</v>
-      </c>
-      <c r="K13">
-        <v>1000</v>
-      </c>
-      <c r="L13" t="s">
-        <v>70</v>
-      </c>
-      <c r="M13" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>204001</v>
+        <v>202006</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="C14">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I14" t="s">
         <v>26</v>
-      </c>
-      <c r="J14">
-        <v>1002</v>
-      </c>
-      <c r="K14">
-        <v>1000</v>
-      </c>
-      <c r="L14" t="s">
-        <v>67</v>
-      </c>
-      <c r="M14" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>204002</v>
+        <v>202007</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="C15">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>57</v>
+        <v>75</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15" t="s">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="I15" t="s">
         <v>26</v>
-      </c>
-      <c r="J15">
-        <v>1004</v>
-      </c>
-      <c r="K15">
-        <v>1000</v>
-      </c>
-      <c r="L15" t="s">
-        <v>68</v>
-      </c>
-      <c r="M15" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>204003</v>
+        <v>203001</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C16">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I16" t="s">
         <v>26</v>
       </c>
       <c r="J16">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="K16">
         <v>1000</v>
       </c>
       <c r="L16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="M16" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>204004</v>
+        <v>203002</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C17">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
       </c>
       <c r="J17">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="K17">
         <v>1000</v>
       </c>
       <c r="L17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M17" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>205001</v>
+        <v>203003</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C18">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
       </c>
       <c r="J18">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="K18">
         <v>1000</v>
       </c>
       <c r="L18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M18" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>205002</v>
+        <v>203004</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C19">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>56</v>
+        <v>76</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I19" t="s">
         <v>26</v>
       </c>
       <c r="J19">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="K19">
         <v>1000</v>
       </c>
       <c r="L19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M19" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>205003</v>
+        <v>203005</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="C20">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>57</v>
+        <v>76</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="I20" t="s">
         <v>26</v>
-      </c>
-      <c r="J20">
-        <v>1006</v>
-      </c>
-      <c r="K20">
-        <v>1000</v>
-      </c>
-      <c r="L20" t="s">
-        <v>69</v>
-      </c>
-      <c r="M20" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21">
+        <v>203006</v>
+      </c>
+      <c r="B21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21">
+        <v>203</v>
+      </c>
+      <c r="D21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21">
+        <v>6</v>
+      </c>
+      <c r="I21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>203007</v>
+      </c>
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22">
+        <v>203</v>
+      </c>
+      <c r="D22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22">
+        <v>7</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>204001</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23">
+        <v>204</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>48</v>
+      </c>
+      <c r="I23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23">
+        <v>1002</v>
+      </c>
+      <c r="K23">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>67</v>
+      </c>
+      <c r="M23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>204002</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24">
+        <v>204</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24">
+        <v>1004</v>
+      </c>
+      <c r="K24">
+        <v>1000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>68</v>
+      </c>
+      <c r="M24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>204003</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25">
+        <v>204</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
+      </c>
+      <c r="H25" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25">
+        <v>1006</v>
+      </c>
+      <c r="K25">
+        <v>1000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>69</v>
+      </c>
+      <c r="M25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>204004</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26">
+        <v>204</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
+      </c>
+      <c r="H26" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26">
+        <v>1008</v>
+      </c>
+      <c r="K26">
+        <v>1000</v>
+      </c>
+      <c r="L26" t="s">
+        <v>70</v>
+      </c>
+      <c r="M26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>204005</v>
+      </c>
+      <c r="B27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27">
+        <v>204</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="I27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>204006</v>
+      </c>
+      <c r="B28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28">
+        <v>204</v>
+      </c>
+      <c r="D28" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+      <c r="I28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>204007</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29">
+        <v>204</v>
+      </c>
+      <c r="D29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29">
+        <v>7</v>
+      </c>
+      <c r="I29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>205001</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30">
+        <v>205</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>48</v>
+      </c>
+      <c r="I30" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30">
+        <v>1002</v>
+      </c>
+      <c r="K30">
+        <v>1000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>67</v>
+      </c>
+      <c r="M30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>205002</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31">
+        <v>205</v>
+      </c>
+      <c r="D31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" t="s">
+        <v>78</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+      <c r="H31" t="s">
+        <v>49</v>
+      </c>
+      <c r="I31" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31">
+        <v>1004</v>
+      </c>
+      <c r="K31">
+        <v>1000</v>
+      </c>
+      <c r="L31" t="s">
+        <v>68</v>
+      </c>
+      <c r="M31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>205003</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32">
+        <v>205</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" t="s">
+        <v>78</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32">
+        <v>1006</v>
+      </c>
+      <c r="K32">
+        <v>1000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>69</v>
+      </c>
+      <c r="M32" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>205004</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B33" t="s">
         <v>47</v>
       </c>
-      <c r="C21">
+      <c r="C33">
         <v>205</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D33" t="s">
         <v>24</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E33" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G21">
+      <c r="G33">
         <v>4</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H33" t="s">
         <v>53</v>
       </c>
-      <c r="I21" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21">
+      <c r="I33" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33">
         <v>1008</v>
       </c>
-      <c r="K21">
+      <c r="K33">
         <v>1000</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L33" t="s">
         <v>70</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M33" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
         <v>210001</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C34" s="2">
         <v>2001</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G34" s="2">
         <v>1</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H34" t="s">
         <v>48</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I34" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" t="s">
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" t="s">
         <v>67</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M34" t="s">
         <v>48</v>
       </c>
     </row>

--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0951BAD-7CB4-49C9-A441-FEE2D9816647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19FF288-156D-4012-8028-E01CC1F46721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="118">
   <si>
     <t>Type</t>
   </si>
@@ -387,6 +387,52 @@
   </si>
   <si>
     <t>보라 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>YellowEngine_5</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>YellowEngine_6</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>YellowEngine_7</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1;0,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1;0,2;1,2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1;0,2;1,2;0,3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1100,8 +1146,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:M34" totalsRowShown="0">
-  <autoFilter ref="A1:M34" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:M37" totalsRowShown="0">
+  <autoFilter ref="A1:M37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Name"/>
@@ -1384,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.75" customWidth="1"/>
@@ -1544,7 +1590,7 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1556,10 +1602,10 @@
         <v>1000</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="M4" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -1585,7 +1631,7 @@
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -1597,10 +1643,10 @@
         <v>1000</v>
       </c>
       <c r="L5" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="M5" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -1625,8 +1671,17 @@
       <c r="G6">
         <v>5</v>
       </c>
+      <c r="H6" t="s">
+        <v>114</v>
+      </c>
       <c r="I6" t="s">
         <v>26</v>
+      </c>
+      <c r="L6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -1651,8 +1706,17 @@
       <c r="G7">
         <v>6</v>
       </c>
+      <c r="H7" t="s">
+        <v>115</v>
+      </c>
       <c r="I7" t="s">
         <v>26</v>
+      </c>
+      <c r="L7" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1677,8 +1741,17 @@
       <c r="G8">
         <v>7</v>
       </c>
+      <c r="H8" t="s">
+        <v>116</v>
+      </c>
       <c r="I8" t="s">
         <v>26</v>
+      </c>
+      <c r="L8" t="s">
+        <v>117</v>
+      </c>
+      <c r="M8" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -2572,39 +2645,117 @@
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="A34">
+        <v>205005</v>
+      </c>
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34">
+        <v>205</v>
+      </c>
+      <c r="D34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="I34" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>205006</v>
+      </c>
+      <c r="B35" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35">
+        <v>205</v>
+      </c>
+      <c r="D35" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" t="s">
+        <v>78</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G35">
+        <v>6</v>
+      </c>
+      <c r="I35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>205007</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C36">
+        <v>205</v>
+      </c>
+      <c r="D36" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G36">
+        <v>7</v>
+      </c>
+      <c r="I36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
         <v>210001</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C37" s="2">
         <v>2001</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G37" s="2">
         <v>1</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H37" t="s">
         <v>48</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" t="s">
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" t="s">
         <v>67</v>
       </c>
-      <c r="M34" t="s">
+      <c r="M37" t="s">
         <v>48</v>
       </c>
     </row>

--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19FF288-156D-4012-8028-E01CC1F46721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B97B1A-535A-45B5-A8CD-C8AAD6B1C81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="150">
   <si>
     <t>Type</t>
   </si>
@@ -189,250 +189,323 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>Icon</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>engine_test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Core</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>core</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>코어</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>코어.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Length</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainCoordinate</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceItemId</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceItemCount</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreenEngine_5</t>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>GreenEngine_6</t>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>GreenEngine_7</t>
+  </si>
+  <si>
+    <t>초록 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>RedEngine_5</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>RedEngine_6</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>RedEngine_7</t>
+  </si>
+  <si>
+    <t>빨강 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>BlueEngine_5</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>BlueEngine_6</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>BlueEngine_7</t>
+  </si>
+  <si>
+    <t>파랑 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>PurpleEngine_5</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>PurpleEngine_6</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>PurpleEngine_7</t>
+  </si>
+  <si>
+    <t>보라 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>YellowEngine_5</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.5</t>
+  </si>
+  <si>
+    <t>YellowEngine_6</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.6</t>
+  </si>
+  <si>
+    <t>YellowEngine_7</t>
+  </si>
+  <si>
+    <t>노랑 엔진 Lv.7</t>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
     <t>0,0;0,1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0</t>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1</t>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1;0,2</t>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1;0,2;1,2</t>
+  </si>
+  <si>
+    <t>0,0;0,1;1,0;1,1;0,2;1,2;0,3</t>
+  </si>
+  <si>
+    <t>0,0;1,0</t>
+  </si>
+  <si>
+    <t>0,0;1,0;2,0</t>
+  </si>
+  <si>
+    <t>0,0;1,0;2,0;1,1</t>
+  </si>
+  <si>
+    <t>0,1;1,1;2,1;1,2;1,0</t>
+  </si>
+  <si>
+    <t>0,1;1,1;2,1;1,2;1,0;0,2</t>
+  </si>
+  <si>
+    <t>0,1;1,1;2,1;1,2;1,0;0,2;2,2</t>
   </si>
   <si>
     <t>0,0;0,1;0,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;0,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;0,2;1,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;0,2;1,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Core</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>core</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>코어</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>코어.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Length</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2;0,3</t>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2;0,3;0,4</t>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2;0,3;0,4;0,5</t>
+  </si>
+  <si>
+    <t>0,0;0,1;0,2;0,3;0,4;0,5;0,6</t>
+  </si>
+  <si>
+    <t>0,0;1,0;2,0;2,1</t>
+  </si>
+  <si>
+    <t>0,1;1,1;2,1;2,2;2,0</t>
+  </si>
+  <si>
+    <t>0,1;1,1;2,1;2,2;2,0;2,3</t>
+  </si>
+  <si>
+    <t>0,2;1,2;2,2;2,3;2,1;2,0;2,4</t>
+  </si>
+  <si>
+    <t>0,0;1,0;1,1</t>
+  </si>
+  <si>
+    <t>0,0;1,0;2,0;2,1;2,2</t>
+  </si>
+  <si>
+    <t>0,0;1,0;2,0;3,0;3,1;3,2</t>
+  </si>
+  <si>
+    <t>0,0;1,0;2,0;3,0;3,1;3,2;3,3</t>
+  </si>
+  <si>
+    <t>#B2EBF2</t>
+  </si>
+  <si>
+    <t>#F4C2C2</t>
+  </si>
+  <si>
+    <t>#B3CCFF</t>
+  </si>
+  <si>
+    <t>#D8BFD8</t>
+  </si>
+  <si>
+    <t>#FFF3B7</t>
   </si>
   <si>
     <t>1,1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>1,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>2,1</t>
+  </si>
+  <si>
+    <t>3,1</t>
+  </si>
+  <si>
+    <t>3,2</t>
+  </si>
+  <si>
+    <t>3,3</t>
   </si>
   <si>
     <t>1,3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainCoordinate</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>1,5</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>1,7</t>
+  </si>
+  <si>
+    <t>3,4</t>
+  </si>
+  <si>
+    <t>3,5</t>
+  </si>
+  <si>
+    <t>4,3</t>
+  </si>
+  <si>
+    <t>4,4</t>
+  </si>
+  <si>
+    <t>1,0</t>
   </si>
   <si>
     <t>0,1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>0,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Green</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Red</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Blue</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Purple</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yellow</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ResourceItemId</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ResourceItemCount</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>GreenEngine_5</t>
-  </si>
-  <si>
-    <t>초록 엔진 Lv.5</t>
-  </si>
-  <si>
-    <t>GreenEngine_6</t>
-  </si>
-  <si>
-    <t>초록 엔진 Lv.6</t>
-  </si>
-  <si>
-    <t>GreenEngine_7</t>
-  </si>
-  <si>
-    <t>초록 엔진 Lv.7</t>
-  </si>
-  <si>
-    <t>RedEngine_5</t>
-  </si>
-  <si>
-    <t>빨강 엔진 Lv.5</t>
-  </si>
-  <si>
-    <t>RedEngine_6</t>
-  </si>
-  <si>
-    <t>빨강 엔진 Lv.6</t>
-  </si>
-  <si>
-    <t>RedEngine_7</t>
-  </si>
-  <si>
-    <t>빨강 엔진 Lv.7</t>
-  </si>
-  <si>
-    <t>BlueEngine_5</t>
-  </si>
-  <si>
-    <t>파랑 엔진 Lv.5</t>
-  </si>
-  <si>
-    <t>BlueEngine_6</t>
-  </si>
-  <si>
-    <t>파랑 엔진 Lv.6</t>
-  </si>
-  <si>
-    <t>BlueEngine_7</t>
-  </si>
-  <si>
-    <t>파랑 엔진 Lv.7</t>
-  </si>
-  <si>
-    <t>PurpleEngine_5</t>
-  </si>
-  <si>
-    <t>보라 엔진 Lv.5</t>
-  </si>
-  <si>
-    <t>PurpleEngine_6</t>
-  </si>
-  <si>
-    <t>보라 엔진 Lv.6</t>
-  </si>
-  <si>
-    <t>PurpleEngine_7</t>
-  </si>
-  <si>
-    <t>보라 엔진 Lv.7</t>
-  </si>
-  <si>
-    <t>YellowEngine_5</t>
-  </si>
-  <si>
-    <t>노랑 엔진 Lv.5</t>
-  </si>
-  <si>
-    <t>YellowEngine_6</t>
-  </si>
-  <si>
-    <t>노랑 엔진 Lv.6</t>
-  </si>
-  <si>
-    <t>YellowEngine_7</t>
-  </si>
-  <si>
-    <t>노랑 엔진 Lv.7</t>
-  </si>
-  <si>
-    <t>0,0;0,1;1,0</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;1,0;1,1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;1,0;1,1;0,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;1,0;1,1;0,2;1,2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,0;0,1;1,0;1,1;0,2;1,2;0,3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,4</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>3,0</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1519,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" t="s">
         <v>27</v>
@@ -1461,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="F1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G1" t="s">
         <v>1</v>
@@ -1473,16 +1546,16 @@
         <v>25</v>
       </c>
       <c r="J1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="K1" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1499,16 +1572,16 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
@@ -1520,10 +1593,10 @@
         <v>1000</v>
       </c>
       <c r="L2" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="M2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1540,16 +1613,16 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
@@ -1561,10 +1634,10 @@
         <v>1000</v>
       </c>
       <c r="L3" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="M3" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1581,16 +1654,16 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1602,10 +1675,10 @@
         <v>1000</v>
       </c>
       <c r="L4" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="M4" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -1622,16 +1695,16 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -1643,10 +1716,10 @@
         <v>1000</v>
       </c>
       <c r="L5" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="M5" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -1654,34 +1727,34 @@
         <v>201005</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C6">
         <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="M6" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -1689,34 +1762,34 @@
         <v>201006</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="M7" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1724,34 +1797,34 @@
         <v>201007</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C8">
         <v>201</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1768,16 +1841,16 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
@@ -1789,10 +1862,10 @@
         <v>1000</v>
       </c>
       <c r="L9" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1809,16 +1882,16 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1830,10 +1903,10 @@
         <v>1000</v>
       </c>
       <c r="L10" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="M10" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1850,16 +1923,16 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G11">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1871,10 +1944,10 @@
         <v>1000</v>
       </c>
       <c r="L11" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="M11" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1891,16 +1964,16 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G12">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1912,10 +1985,10 @@
         <v>1000</v>
       </c>
       <c r="L12" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="M12" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1923,25 +1996,34 @@
         <v>202005</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C13">
         <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
+      <c r="H13" t="s">
+        <v>105</v>
+      </c>
       <c r="I13" t="s">
         <v>26</v>
+      </c>
+      <c r="L13" t="s">
+        <v>134</v>
+      </c>
+      <c r="M13" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -1949,25 +2031,34 @@
         <v>202006</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C14">
         <v>202</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G14">
         <v>6</v>
       </c>
+      <c r="H14" t="s">
+        <v>106</v>
+      </c>
       <c r="I14" t="s">
         <v>26</v>
+      </c>
+      <c r="L14" t="s">
+        <v>134</v>
+      </c>
+      <c r="M14" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1975,25 +2066,34 @@
         <v>202007</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="C15">
         <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G15">
         <v>7</v>
       </c>
+      <c r="H15" t="s">
+        <v>107</v>
+      </c>
       <c r="I15" t="s">
         <v>26</v>
+      </c>
+      <c r="L15" t="s">
+        <v>134</v>
+      </c>
+      <c r="M15" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -2010,16 +2110,16 @@
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s">
         <v>26</v>
@@ -2031,10 +2131,10 @@
         <v>1000</v>
       </c>
       <c r="L16" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="M16" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -2051,16 +2151,16 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
@@ -2072,10 +2172,10 @@
         <v>1000</v>
       </c>
       <c r="L17" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="M17" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -2092,16 +2192,16 @@
         <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G18">
         <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
@@ -2113,10 +2213,10 @@
         <v>1000</v>
       </c>
       <c r="L18" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -2133,16 +2233,16 @@
         <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G19">
         <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="I19" t="s">
         <v>26</v>
@@ -2154,10 +2254,10 @@
         <v>1000</v>
       </c>
       <c r="L19" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="M19" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -2165,25 +2265,34 @@
         <v>203005</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C20">
         <v>203</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
+      <c r="H20" t="s">
+        <v>110</v>
+      </c>
       <c r="I20" t="s">
         <v>26</v>
+      </c>
+      <c r="L20" t="s">
+        <v>137</v>
+      </c>
+      <c r="M20" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -2191,25 +2300,34 @@
         <v>203006</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C21">
         <v>203</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G21">
         <v>6</v>
       </c>
+      <c r="H21" t="s">
+        <v>111</v>
+      </c>
       <c r="I21" t="s">
         <v>26</v>
+      </c>
+      <c r="L21" t="s">
+        <v>138</v>
+      </c>
+      <c r="M21" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -2217,25 +2335,34 @@
         <v>203007</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C22">
         <v>203</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G22">
         <v>7</v>
       </c>
+      <c r="H22" t="s">
+        <v>112</v>
+      </c>
       <c r="I22" t="s">
         <v>26</v>
+      </c>
+      <c r="L22" t="s">
+        <v>139</v>
+      </c>
+      <c r="M22" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -2252,16 +2379,16 @@
         <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s">
         <v>26</v>
@@ -2273,10 +2400,10 @@
         <v>1000</v>
       </c>
       <c r="L23" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="M23" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -2293,16 +2420,16 @@
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="I24" t="s">
         <v>26</v>
@@ -2314,10 +2441,10 @@
         <v>1000</v>
       </c>
       <c r="L24" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="M24" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -2334,16 +2461,16 @@
         <v>19</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G25">
         <v>3</v>
       </c>
       <c r="H25" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -2355,10 +2482,10 @@
         <v>1000</v>
       </c>
       <c r="L25" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="M25" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -2375,16 +2502,16 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="I26" t="s">
         <v>26</v>
@@ -2396,10 +2523,10 @@
         <v>1000</v>
       </c>
       <c r="L26" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="M26" t="s">
-        <v>73</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
@@ -2407,25 +2534,34 @@
         <v>204005</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C27">
         <v>204</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
+      <c r="H27" t="s">
+        <v>114</v>
+      </c>
       <c r="I27" t="s">
         <v>26</v>
+      </c>
+      <c r="L27" t="s">
+        <v>134</v>
+      </c>
+      <c r="M27" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -2433,25 +2569,34 @@
         <v>204006</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C28">
         <v>204</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G28">
         <v>6</v>
       </c>
+      <c r="H28" t="s">
+        <v>115</v>
+      </c>
       <c r="I28" t="s">
         <v>26</v>
+      </c>
+      <c r="L28" t="s">
+        <v>140</v>
+      </c>
+      <c r="M28" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -2459,25 +2604,34 @@
         <v>204007</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C29">
         <v>204</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G29">
         <v>7</v>
       </c>
+      <c r="H29" t="s">
+        <v>116</v>
+      </c>
       <c r="I29" t="s">
         <v>26</v>
+      </c>
+      <c r="L29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M29" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -2494,16 +2648,16 @@
         <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s">
         <v>26</v>
@@ -2515,10 +2669,10 @@
         <v>1000</v>
       </c>
       <c r="L30" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="M30" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
@@ -2535,16 +2689,16 @@
         <v>22</v>
       </c>
       <c r="E31" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="I31" t="s">
         <v>26</v>
@@ -2556,10 +2710,10 @@
         <v>1000</v>
       </c>
       <c r="L31" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="M31" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
@@ -2576,16 +2730,16 @@
         <v>23</v>
       </c>
       <c r="E32" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G32">
         <v>3</v>
       </c>
       <c r="H32" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
@@ -2597,10 +2751,10 @@
         <v>1000</v>
       </c>
       <c r="L32" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="M32" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -2617,16 +2771,16 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G33">
         <v>4</v>
       </c>
       <c r="H33" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
@@ -2638,10 +2792,10 @@
         <v>1000</v>
       </c>
       <c r="L33" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="M33" t="s">
-        <v>73</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -2649,25 +2803,34 @@
         <v>205005</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C34">
         <v>205</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E34" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G34">
         <v>5</v>
       </c>
+      <c r="H34" t="s">
+        <v>118</v>
+      </c>
       <c r="I34" t="s">
         <v>26</v>
+      </c>
+      <c r="L34" t="s">
+        <v>134</v>
+      </c>
+      <c r="M34" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
@@ -2675,25 +2838,34 @@
         <v>205006</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C35">
         <v>205</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="E35" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G35">
         <v>6</v>
       </c>
+      <c r="H35" t="s">
+        <v>119</v>
+      </c>
       <c r="I35" t="s">
         <v>26</v>
+      </c>
+      <c r="L35" t="s">
+        <v>142</v>
+      </c>
+      <c r="M35" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -2701,25 +2873,34 @@
         <v>205007</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C36">
         <v>205</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G36">
         <v>7</v>
       </c>
+      <c r="H36" t="s">
+        <v>120</v>
+      </c>
       <c r="I36" t="s">
         <v>26</v>
+      </c>
+      <c r="L36" t="s">
+        <v>143</v>
+      </c>
+      <c r="M36" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
@@ -2727,19 +2908,19 @@
         <v>210001</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C37" s="2">
         <v>2001</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G37" s="2">
         <v>1</v>
@@ -2748,12 +2929,12 @@
         <v>48</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="M37" t="s">
         <v>48</v>

--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B97B1A-535A-45B5-A8CD-C8AAD6B1C81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258CB219-0C49-490A-B655-FE76BC354F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1750,6 +1750,9 @@
       <c r="I6" t="s">
         <v>26</v>
       </c>
+      <c r="J6">
+        <v>1010</v>
+      </c>
       <c r="L6" t="s">
         <v>129</v>
       </c>
@@ -1785,6 +1788,9 @@
       <c r="I7" t="s">
         <v>26</v>
       </c>
+      <c r="J7">
+        <v>1012</v>
+      </c>
       <c r="L7" t="s">
         <v>129</v>
       </c>
@@ -1820,6 +1826,9 @@
       <c r="I8" t="s">
         <v>26</v>
       </c>
+      <c r="J8">
+        <v>1014</v>
+      </c>
       <c r="L8" t="s">
         <v>130</v>
       </c>
@@ -2019,6 +2028,12 @@
       <c r="I13" t="s">
         <v>26</v>
       </c>
+      <c r="J13">
+        <v>1010</v>
+      </c>
+      <c r="K13">
+        <v>1000</v>
+      </c>
       <c r="L13" t="s">
         <v>134</v>
       </c>
@@ -2054,6 +2069,12 @@
       <c r="I14" t="s">
         <v>26</v>
       </c>
+      <c r="J14">
+        <v>1012</v>
+      </c>
+      <c r="K14">
+        <v>1000</v>
+      </c>
       <c r="L14" t="s">
         <v>134</v>
       </c>
@@ -2089,6 +2110,12 @@
       <c r="I15" t="s">
         <v>26</v>
       </c>
+      <c r="J15">
+        <v>1014</v>
+      </c>
+      <c r="K15">
+        <v>1000</v>
+      </c>
       <c r="L15" t="s">
         <v>134</v>
       </c>
@@ -2288,6 +2315,12 @@
       <c r="I20" t="s">
         <v>26</v>
       </c>
+      <c r="J20">
+        <v>1010</v>
+      </c>
+      <c r="K20">
+        <v>1000</v>
+      </c>
       <c r="L20" t="s">
         <v>137</v>
       </c>
@@ -2323,6 +2356,12 @@
       <c r="I21" t="s">
         <v>26</v>
       </c>
+      <c r="J21">
+        <v>1012</v>
+      </c>
+      <c r="K21">
+        <v>1000</v>
+      </c>
       <c r="L21" t="s">
         <v>138</v>
       </c>
@@ -2358,6 +2397,12 @@
       <c r="I22" t="s">
         <v>26</v>
       </c>
+      <c r="J22">
+        <v>1014</v>
+      </c>
+      <c r="K22">
+        <v>1000</v>
+      </c>
       <c r="L22" t="s">
         <v>139</v>
       </c>
@@ -2557,6 +2602,12 @@
       <c r="I27" t="s">
         <v>26</v>
       </c>
+      <c r="J27">
+        <v>1010</v>
+      </c>
+      <c r="K27">
+        <v>1000</v>
+      </c>
       <c r="L27" t="s">
         <v>134</v>
       </c>
@@ -2592,6 +2643,12 @@
       <c r="I28" t="s">
         <v>26</v>
       </c>
+      <c r="J28">
+        <v>1012</v>
+      </c>
+      <c r="K28">
+        <v>1000</v>
+      </c>
       <c r="L28" t="s">
         <v>140</v>
       </c>
@@ -2627,6 +2684,12 @@
       <c r="I29" t="s">
         <v>26</v>
       </c>
+      <c r="J29">
+        <v>1014</v>
+      </c>
+      <c r="K29">
+        <v>1000</v>
+      </c>
       <c r="L29" t="s">
         <v>141</v>
       </c>
@@ -2826,6 +2889,12 @@
       <c r="I34" t="s">
         <v>26</v>
       </c>
+      <c r="J34">
+        <v>1010</v>
+      </c>
+      <c r="K34">
+        <v>1000</v>
+      </c>
       <c r="L34" t="s">
         <v>134</v>
       </c>
@@ -2861,6 +2930,12 @@
       <c r="I35" t="s">
         <v>26</v>
       </c>
+      <c r="J35">
+        <v>1012</v>
+      </c>
+      <c r="K35">
+        <v>1000</v>
+      </c>
       <c r="L35" t="s">
         <v>142</v>
       </c>
@@ -2895,6 +2970,12 @@
       </c>
       <c r="I36" t="s">
         <v>26</v>
+      </c>
+      <c r="J36">
+        <v>1014</v>
+      </c>
+      <c r="K36">
+        <v>1000</v>
       </c>
       <c r="L36" t="s">
         <v>143</v>

--- a/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
+++ b/Assets/100_Data/XlsxFiles/Engine_Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koseonghyeon\Desktop\Drill_Game\Drill_game\Assets\100_Data\XlsxFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Coding\Drill_Game\Assets\100_Data\XlsxFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258CB219-0C49-490A-B655-FE76BC354F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Engine_Data" sheetId="1" r:id="rId1"/>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="151">
   <si>
     <t>Type</t>
   </si>
@@ -197,22 +196,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>engine_test</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Core</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -506,12 +489,32 @@
   </si>
   <si>
     <t>3,0</t>
+  </si>
+  <si>
+    <t>greenEngine</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>redEngine</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>blueEngine</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>purpleEngine</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellowEngine</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1219,22 +1222,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:M37" totalsRowShown="0">
-  <autoFilter ref="A1:M37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A1:M37" totalsRowShown="0">
+  <autoFilter ref="A1:M37"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Name"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="EngineId"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="DisplayName"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Icon"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Level"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Coordinates"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Desc"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="ResourceItemId"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="ResourceItemCount"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Length"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="MainCoordinate"/>
+    <tableColumn id="1" name="Id"/>
+    <tableColumn id="8" name="Name"/>
+    <tableColumn id="6" name="EngineId"/>
+    <tableColumn id="5" name="DisplayName"/>
+    <tableColumn id="2" name="Type"/>
+    <tableColumn id="9" name="Icon"/>
+    <tableColumn id="3" name="Level"/>
+    <tableColumn id="4" name="Coordinates"/>
+    <tableColumn id="7" name="Desc"/>
+    <tableColumn id="12" name="ResourceItemId"/>
+    <tableColumn id="13" name="ResourceItemCount"/>
+    <tableColumn id="10" name="Length"/>
+    <tableColumn id="11" name="MainCoordinate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1502,7 +1505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1519,7 +1522,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B1" t="s">
         <v>27</v>
@@ -1546,16 +1549,16 @@
         <v>25</v>
       </c>
       <c r="J1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -1572,16 +1575,16 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I2" t="s">
         <v>26</v>
@@ -1593,10 +1596,10 @@
         <v>1000</v>
       </c>
       <c r="L2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1613,16 +1616,16 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>51</v>
+        <v>117</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="G3">
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
@@ -1634,10 +1637,10 @@
         <v>1000</v>
       </c>
       <c r="L3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1654,16 +1657,16 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1675,10 +1678,10 @@
         <v>1000</v>
       </c>
       <c r="L4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -1695,16 +1698,16 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>50</v>
+        <v>117</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -1716,10 +1719,10 @@
         <v>1000</v>
       </c>
       <c r="L5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -1727,25 +1730,25 @@
         <v>201005</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
@@ -1754,10 +1757,10 @@
         <v>1010</v>
       </c>
       <c r="L6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -1765,25 +1768,25 @@
         <v>201006</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>50</v>
+        <v>117</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="G7">
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
@@ -1792,10 +1795,10 @@
         <v>1012</v>
       </c>
       <c r="L7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1803,25 +1806,25 @@
         <v>201007</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C8">
         <v>201</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="G8">
         <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1830,10 +1833,10 @@
         <v>1014</v>
       </c>
       <c r="L8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1850,16 +1853,16 @@
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
@@ -1871,10 +1874,10 @@
         <v>1000</v>
       </c>
       <c r="L9" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1891,16 +1894,16 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>50</v>
+        <v>118</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1912,10 +1915,10 @@
         <v>1000</v>
       </c>
       <c r="L10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1932,16 +1935,16 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="G11">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1953,10 +1956,10 @@
         <v>1000</v>
       </c>
       <c r="L11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M11" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1973,16 +1976,16 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>50</v>
+        <v>118</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="G12">
         <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1994,10 +1997,10 @@
         <v>1000</v>
       </c>
       <c r="L12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -2005,25 +2008,25 @@
         <v>202005</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C13">
         <v>202</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
@@ -2035,10 +2038,10 @@
         <v>1000</v>
       </c>
       <c r="L13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -2046,25 +2049,25 @@
         <v>202006</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C14">
         <v>202</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>122</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>50</v>
+        <v>118</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="G14">
         <v>6</v>
       </c>
       <c r="H14" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I14" t="s">
         <v>26</v>
@@ -2076,10 +2079,10 @@
         <v>1000</v>
       </c>
       <c r="L14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -2087,25 +2090,25 @@
         <v>202007</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C15">
         <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="G15">
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I15" t="s">
         <v>26</v>
@@ -2117,10 +2120,10 @@
         <v>1000</v>
       </c>
       <c r="L15" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -2137,16 +2140,16 @@
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s">
         <v>26</v>
@@ -2158,10 +2161,10 @@
         <v>1000</v>
       </c>
       <c r="L16" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -2178,16 +2181,16 @@
         <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>54</v>
+        <v>119</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="G17">
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
@@ -2199,10 +2202,10 @@
         <v>1000</v>
       </c>
       <c r="L17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -2219,16 +2222,16 @@
         <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="G18">
         <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
@@ -2240,10 +2243,10 @@
         <v>1000</v>
       </c>
       <c r="L18" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M18" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -2260,16 +2263,16 @@
         <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>54</v>
+        <v>119</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="G19">
         <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I19" t="s">
         <v>26</v>
@@ -2281,10 +2284,10 @@
         <v>1000</v>
       </c>
       <c r="L19" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="M19" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -2292,25 +2295,25 @@
         <v>203005</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>203</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="G20">
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I20" t="s">
         <v>26</v>
@@ -2322,10 +2325,10 @@
         <v>1000</v>
       </c>
       <c r="L20" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M20" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -2333,25 +2336,25 @@
         <v>203006</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C21">
         <v>203</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>123</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>50</v>
+        <v>119</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="G21">
         <v>6</v>
       </c>
       <c r="H21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I21" t="s">
         <v>26</v>
@@ -2363,10 +2366,10 @@
         <v>1000</v>
       </c>
       <c r="L21" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -2374,25 +2377,25 @@
         <v>203007</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C22">
         <v>203</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E22" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="G22">
         <v>7</v>
       </c>
       <c r="H22" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I22" t="s">
         <v>26</v>
@@ -2404,10 +2407,10 @@
         <v>1000</v>
       </c>
       <c r="L22" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M22" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -2424,16 +2427,16 @@
         <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s">
         <v>26</v>
@@ -2445,10 +2448,10 @@
         <v>1000</v>
       </c>
       <c r="L23" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M23" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -2465,16 +2468,16 @@
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>51</v>
+        <v>120</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I24" t="s">
         <v>26</v>
@@ -2486,10 +2489,10 @@
         <v>1000</v>
       </c>
       <c r="L24" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M24" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -2506,16 +2509,16 @@
         <v>19</v>
       </c>
       <c r="E25" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="G25">
         <v>3</v>
       </c>
       <c r="H25" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -2527,10 +2530,10 @@
         <v>1000</v>
       </c>
       <c r="L25" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M25" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -2547,16 +2550,16 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>50</v>
+        <v>120</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I26" t="s">
         <v>26</v>
@@ -2568,10 +2571,10 @@
         <v>1000</v>
       </c>
       <c r="L26" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M26" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
@@ -2579,25 +2582,25 @@
         <v>204005</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C27">
         <v>204</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="G27">
         <v>5</v>
       </c>
       <c r="H27" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I27" t="s">
         <v>26</v>
@@ -2609,10 +2612,10 @@
         <v>1000</v>
       </c>
       <c r="L27" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M27" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -2620,25 +2623,25 @@
         <v>204006</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C28">
         <v>204</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>50</v>
+        <v>120</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="G28">
         <v>6</v>
       </c>
       <c r="H28" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
@@ -2650,10 +2653,10 @@
         <v>1000</v>
       </c>
       <c r="L28" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M28" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -2661,25 +2664,25 @@
         <v>204007</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C29">
         <v>204</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="G29">
         <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I29" t="s">
         <v>26</v>
@@ -2691,10 +2694,10 @@
         <v>1000</v>
       </c>
       <c r="L29" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="M29" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -2711,16 +2714,16 @@
         <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I30" t="s">
         <v>26</v>
@@ -2732,10 +2735,10 @@
         <v>1000</v>
       </c>
       <c r="L30" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
@@ -2752,16 +2755,16 @@
         <v>22</v>
       </c>
       <c r="E31" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I31" t="s">
         <v>26</v>
@@ -2773,10 +2776,10 @@
         <v>1000</v>
       </c>
       <c r="L31" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M31" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
@@ -2793,16 +2796,16 @@
         <v>23</v>
       </c>
       <c r="E32" t="s">
-        <v>125</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>51</v>
+        <v>121</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="G32">
         <v>3</v>
       </c>
       <c r="H32" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
@@ -2814,10 +2817,10 @@
         <v>1000</v>
       </c>
       <c r="L32" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M32" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -2834,16 +2837,16 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G33">
         <v>4</v>
       </c>
       <c r="H33" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
@@ -2855,10 +2858,10 @@
         <v>1000</v>
       </c>
       <c r="L33" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M33" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
@@ -2866,25 +2869,25 @@
         <v>205005</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C34">
         <v>205</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E34" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G34">
         <v>5</v>
       </c>
       <c r="H34" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I34" t="s">
         <v>26</v>
@@ -2896,10 +2899,10 @@
         <v>1000</v>
       </c>
       <c r="L34" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="M34" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
@@ -2907,25 +2910,25 @@
         <v>205006</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C35">
         <v>205</v>
       </c>
       <c r="D35" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E35" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G35">
         <v>6</v>
       </c>
       <c r="H35" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
@@ -2937,10 +2940,10 @@
         <v>1000</v>
       </c>
       <c r="L35" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="M35" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -2948,25 +2951,25 @@
         <v>205007</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C36">
         <v>205</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>50</v>
+        <v>121</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="G36">
         <v>7</v>
       </c>
       <c r="H36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
@@ -2978,10 +2981,10 @@
         <v>1000</v>
       </c>
       <c r="L36" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M36" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
@@ -2989,16 +2992,16 @@
         <v>210001</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C37" s="2">
         <v>2001</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>50</v>
@@ -3010,12 +3013,12 @@
         <v>48</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M37" t="s">
         <v>48</v>
